--- a/assets/visual-resource/stock/UCV2_l3k3JuZwIhiY1H0kSxA/UCV2_l3k3JuZwIhiY1H0kSxA.xlsx
+++ b/assets/visual-resource/stock/UCV2_l3k3JuZwIhiY1H0kSxA/UCV2_l3k3JuZwIhiY1H0kSxA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="326">
   <si>
     <t>LINK</t>
   </si>
@@ -22,10 +22,973 @@
     <t>USED</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=HPIGJ4UftDs</t>
-  </si>
-  <si>
-    <t>00:09:51</t>
+    <t>https://www.youtube.com/watch?v=MMYJaegO774</t>
+  </si>
+  <si>
+    <t>00:37:40</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hVMT9DFBiXw</t>
+  </si>
+  <si>
+    <t>00:30:37</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hS6vjAqLCV0</t>
+  </si>
+  <si>
+    <t>00:38:08</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EsCmj7NMwoE</t>
+  </si>
+  <si>
+    <t>01:10:18</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=oA7JL7pF9Is</t>
+  </si>
+  <si>
+    <t>00:30:12</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vq7txQJcrxE</t>
+  </si>
+  <si>
+    <t>01:00:06</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CTfoS0pSn00</t>
+  </si>
+  <si>
+    <t>00:40:54</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wZKTsYW8BoU</t>
+  </si>
+  <si>
+    <t>00:31:48</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nKuvFUcqf7o</t>
+  </si>
+  <si>
+    <t>00:35:15</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HBuv95C64z8</t>
+  </si>
+  <si>
+    <t>00:30:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=a_PaSxIyKfw</t>
+  </si>
+  <si>
+    <t>00:43:24</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JgwLvzHoG-s</t>
+  </si>
+  <si>
+    <t>00:32:07</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=U_W-ykWsgOA</t>
+  </si>
+  <si>
+    <t>02:17:19</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LddoNrTyJA4</t>
+  </si>
+  <si>
+    <t>00:54:40</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kWuW-tJ-kzQ</t>
+  </si>
+  <si>
+    <t>01:11:54</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mcqtvSt_Wwg</t>
+  </si>
+  <si>
+    <t>02:11:09</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-9U8HdvYSWA</t>
+  </si>
+  <si>
+    <t>01:07:37</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2Uv-j4s482U</t>
+  </si>
+  <si>
+    <t>01:16:12</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SE_oGfR3krQ</t>
+  </si>
+  <si>
+    <t>01:17:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JDvLlvPDhxg</t>
+  </si>
+  <si>
+    <t>00:59:31</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nhpp-ZokXT8</t>
+  </si>
+  <si>
+    <t>01:18:30</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lL2mFfR_0XI</t>
+  </si>
+  <si>
+    <t>01:08:10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iQ2RXLUH9mI</t>
+  </si>
+  <si>
+    <t>00:45:40</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1F6sQHXvZqE</t>
+  </si>
+  <si>
+    <t>01:03:48</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6Yn5nBsueIk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KQj0sYawcA0</t>
+  </si>
+  <si>
+    <t>01:58:14</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QVkVZlf1TSM</t>
+  </si>
+  <si>
+    <t>03:01:54</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sTs9aa7Y6lI</t>
+  </si>
+  <si>
+    <t>02:43:01</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dwNOm2oc1sc</t>
+  </si>
+  <si>
+    <t>01:36:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4Poc7RVTk08</t>
+  </si>
+  <si>
+    <t>01:51:48</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IJAG7sR-tms</t>
+  </si>
+  <si>
+    <t>01:33:45</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LkGZg8rdE-o</t>
+  </si>
+  <si>
+    <t>01:25:42</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kVizV-oQOfI</t>
+  </si>
+  <si>
+    <t>01:20:40</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Gwfq7moxzKw</t>
+  </si>
+  <si>
+    <t>03:44:32</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-iGqSdrfejw</t>
+  </si>
+  <si>
+    <t>01:20:58</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VZrcZLJ0HUM</t>
+  </si>
+  <si>
+    <t>03:49:28</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VvBy52kYmAQ</t>
+  </si>
+  <si>
+    <t>03:43:12</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nw9uApBSoWI</t>
+  </si>
+  <si>
+    <t>02:49:34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mD1J68ce2-s</t>
+  </si>
+  <si>
+    <t>04:11:50</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8ozcWp5Bj4c</t>
+  </si>
+  <si>
+    <t>02:36:18</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vxiJHOWmp7o</t>
+  </si>
+  <si>
+    <t>01:36:00</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yfkawsGbt64</t>
+  </si>
+  <si>
+    <t>04:28:59</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qyp9N9xtlb4</t>
+  </si>
+  <si>
+    <t>01:23:44</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Mm_EC-RVgPY</t>
+  </si>
+  <si>
+    <t>02:09:31</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CVN51hrczUc</t>
+  </si>
+  <si>
+    <t>01:58:07</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ciDEQnuLVfE</t>
+  </si>
+  <si>
+    <t>01:58:34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7oBKQO9kVPg</t>
+  </si>
+  <si>
+    <t>01:32:50</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TAJUgB2Uc-A</t>
+  </si>
+  <si>
+    <t>03:40:44</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=U0NhHuQ9HbE</t>
+  </si>
+  <si>
+    <t>02:27:20</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MTkX0_htW-I</t>
+  </si>
+  <si>
+    <t>02:13:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nnm6qsXOnEk</t>
+  </si>
+  <si>
+    <t>03:33:30</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AM8MsJWuevw</t>
+  </si>
+  <si>
+    <t>01:03:07</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F6bdMoGEAz8</t>
+  </si>
+  <si>
+    <t>03:57:54</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UJw2HGqlHPg</t>
+  </si>
+  <si>
+    <t>01:20:03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=I0s0xVRERs0</t>
+  </si>
+  <si>
+    <t>02:43:07</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rmxNPzpuFB4</t>
+  </si>
+  <si>
+    <t>01:48:37</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=d3lX1iSEkT8</t>
+  </si>
+  <si>
+    <t>03:11:10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mt6uleO1tEs</t>
+  </si>
+  <si>
+    <t>02:14:51</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bmyL56iKBLI</t>
+  </si>
+  <si>
+    <t>02:49:16</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sq0fi9y9iKY</t>
+  </si>
+  <si>
+    <t>03:09:09</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IqT-VrrptPs</t>
+  </si>
+  <si>
+    <t>01:22:23</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ClarmAxEZGk</t>
+  </si>
+  <si>
+    <t>01:32:09</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3MFlpVe93XU</t>
+  </si>
+  <si>
+    <t>03:01:13</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=I9XB1gHvF74</t>
+  </si>
+  <si>
+    <t>03:35:35</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aFNLlmw0zi8</t>
+  </si>
+  <si>
+    <t>00:49:35</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Prz2VJOdtEE</t>
+  </si>
+  <si>
+    <t>03:24:45</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_9g4OLdUkvU</t>
+  </si>
+  <si>
+    <t>03:06:24</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=48PXW6V8Cj4</t>
+  </si>
+  <si>
+    <t>01:14:30</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bCwUwTcvT2M</t>
+  </si>
+  <si>
+    <t>02:46:22</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YXjRnctheXA</t>
+  </si>
+  <si>
+    <t>01:48:21</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WHl2fyeoRKo</t>
+  </si>
+  <si>
+    <t>00:47:05</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3_o9H1f8H5s</t>
+  </si>
+  <si>
+    <t>01:08:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=saRic7RKpdo</t>
+  </si>
+  <si>
+    <t>01:33:15</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=V9HIt9Cbfb0</t>
+  </si>
+  <si>
+    <t>01:46:00</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xJVOVzK03BQ</t>
+  </si>
+  <si>
+    <t>02:06:02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Tlqv2y69Wgo</t>
+  </si>
+  <si>
+    <t>02:14:19</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6BPuGeS6O4w</t>
+  </si>
+  <si>
+    <t>01:44:59</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CgyP8H1Wy7Q</t>
+  </si>
+  <si>
+    <t>01:09:37</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8DgYH9OXARI</t>
+  </si>
+  <si>
+    <t>03:36:21</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OnGu5XgeZ3E</t>
+  </si>
+  <si>
+    <t>03:08:51</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3ecyAHQDsIU</t>
+  </si>
+  <si>
+    <t>02:37:32</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=queARn1XaCc</t>
+  </si>
+  <si>
+    <t>02:49:29</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=A-eMiEiTdc4</t>
+  </si>
+  <si>
+    <t>03:07:34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=r11kS1unliM</t>
+  </si>
+  <si>
+    <t>02:04:24</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Z8SuL0R8dGI</t>
+  </si>
+  <si>
+    <t>03:31:12</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0h0vHA4-XG4</t>
+  </si>
+  <si>
+    <t>02:46:03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GzBPdJT8rq4</t>
+  </si>
+  <si>
+    <t>02:10:02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vfB6rAlV9Xc</t>
+  </si>
+  <si>
+    <t>03:24:54</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aqevs6jLdJI</t>
+  </si>
+  <si>
+    <t>03:53:07</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jQsWHOXz-W4</t>
+  </si>
+  <si>
+    <t>02:14:10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gCy1x1ncd0E</t>
+  </si>
+  <si>
+    <t>02:22:34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=n_hx_rQQ6sw</t>
+  </si>
+  <si>
+    <t>03:19:40</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vklLgAAwt4g</t>
+  </si>
+  <si>
+    <t>02:11:35</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AWOW1-TQbKQ</t>
+  </si>
+  <si>
+    <t>02:27:03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=L2MgUmyndng</t>
+  </si>
+  <si>
+    <t>01:29:18</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TKNK0c1zfVo</t>
+  </si>
+  <si>
+    <t>01:04:14</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RH052bZ6J1k</t>
+  </si>
+  <si>
+    <t>01:09:46</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Dtqqm8zZr5A</t>
+  </si>
+  <si>
+    <t>03:03:22</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LV5cGYJWZYY</t>
+  </si>
+  <si>
+    <t>04:30:21</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GTi2D70oVEk</t>
+  </si>
+  <si>
+    <t>01:31:26</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0Bm3yzv87n4</t>
+  </si>
+  <si>
+    <t>03:12:13</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HrS3SWIUyJY</t>
+  </si>
+  <si>
+    <t>01:58:29</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_OZhGsKdBYY</t>
+  </si>
+  <si>
+    <t>02:53:14</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MvAOBpB6s3s</t>
+  </si>
+  <si>
+    <t>01:00:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kKL7C8UT_LQ</t>
+  </si>
+  <si>
+    <t>02:47:30</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=b4VLlbM_qHI</t>
+  </si>
+  <si>
+    <t>01:31:42</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4R1igX91de8</t>
+  </si>
+  <si>
+    <t>02:47:46</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RZ9ZeSu8HIE</t>
+  </si>
+  <si>
+    <t>04:40:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3CRJWy5zXvg</t>
+  </si>
+  <si>
+    <t>01:42:46</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8PHsbE8iVYM</t>
+  </si>
+  <si>
+    <t>01:45:11</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Md6HD5Z3M-M</t>
+  </si>
+  <si>
+    <t>01:31:49</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xfJxNlxmTsc</t>
+  </si>
+  <si>
+    <t>03:16:45</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=thncN0KR_dE</t>
+  </si>
+  <si>
+    <t>05:37:56</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zvc7ZcMmIWE</t>
+  </si>
+  <si>
+    <t>04:44:46</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=64iJylQa0Y4</t>
+  </si>
+  <si>
+    <t>03:08:24</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ot-HMv_PKs0</t>
+  </si>
+  <si>
+    <t>04:24:36</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7qz13Chz_84</t>
+  </si>
+  <si>
+    <t>02:36:43</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=npTBK0VmhxI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kG8VECrip1o</t>
+  </si>
+  <si>
+    <t>01:14:10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ze42hH2GzHc</t>
+  </si>
+  <si>
+    <t>03:32:59</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=50z58XAVBgc</t>
+  </si>
+  <si>
+    <t>03:50:49</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JU8axX1s8qY</t>
+  </si>
+  <si>
+    <t>02:09:46</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CAsklz0e0_Q</t>
+  </si>
+  <si>
+    <t>01:51:05</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kjN9Ip8idbU</t>
+  </si>
+  <si>
+    <t>01:24:26</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-F-agNdrY2Q</t>
+  </si>
+  <si>
+    <t>02:11:22</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hzcjudnfY9o</t>
+  </si>
+  <si>
+    <t>01:39:52</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8FCkb7NZ7SI</t>
+  </si>
+  <si>
+    <t>02:20:28</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=arOQ7slh3pM</t>
+  </si>
+  <si>
+    <t>01:11:42</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-fvwoh88vAI</t>
+  </si>
+  <si>
+    <t>02:02:49</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pbBA2oAuLRY</t>
+  </si>
+  <si>
+    <t>01:39:05</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SYzzp-khjiQ</t>
+  </si>
+  <si>
+    <t>03:07:35</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VrP2-ijDn9Y</t>
+  </si>
+  <si>
+    <t>00:41:47</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KsNxFH0B0BI</t>
+  </si>
+  <si>
+    <t>01:02:12</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8WlUiln-VeY</t>
+  </si>
+  <si>
+    <t>04:43:36</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ugK4uFs_E1g</t>
+  </si>
+  <si>
+    <t>02:27:52</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hbG_FrOsPFA</t>
+  </si>
+  <si>
+    <t>01:24:51</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nNCrh_f4Hdc</t>
+  </si>
+  <si>
+    <t>03:00:38</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NON14NgRTC4</t>
+  </si>
+  <si>
+    <t>03:02:01</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BbE0Bv2-R50</t>
+  </si>
+  <si>
+    <t>01:25:28</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AsuDyA2GZFc</t>
+  </si>
+  <si>
+    <t>03:06:10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5ieD4hXK7ng</t>
+  </si>
+  <si>
+    <t>03:12:04</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nbQ_z-0ZO28</t>
+  </si>
+  <si>
+    <t>01:14:02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AvvKx5IVbFc</t>
+  </si>
+  <si>
+    <t>00:47:49</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ovK5FbRXVkg</t>
+  </si>
+  <si>
+    <t>00:33:57</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Qgo8GWMsKIc</t>
+  </si>
+  <si>
+    <t>01:01:33</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=35y7ZrX1dAQ</t>
+  </si>
+  <si>
+    <t>04:26:10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Rj_DWpzBxOc</t>
+  </si>
+  <si>
+    <t>02:03:37</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XqFyxqHibyk</t>
+  </si>
+  <si>
+    <t>00:53:34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MUuvD2DiwJw</t>
+  </si>
+  <si>
+    <t>02:15:08</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OImKEFPyT7E</t>
+  </si>
+  <si>
+    <t>02:45:49</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nvrlH6lFBwk</t>
+  </si>
+  <si>
+    <t>00:43:12</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VINOSu5y4ic</t>
+  </si>
+  <si>
+    <t>04:05:43</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fVh9YNTzhak</t>
+  </si>
+  <si>
+    <t>03:10:14</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_SVv-YROSXI</t>
+  </si>
+  <si>
+    <t>01:43:22</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=a5nupxNx3k8</t>
+  </si>
+  <si>
+    <t>00:56:28</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cH1E97JIyUo</t>
+  </si>
+  <si>
+    <t>03:36:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cti-fIP6LAA</t>
+  </si>
+  <si>
+    <t>00:58:13</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0IZ42l3QASE</t>
+  </si>
+  <si>
+    <t>00:46:18</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YHzylyxiAMM</t>
+  </si>
+  <si>
+    <t>00:36:25</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JTz8KNKgAhk</t>
+  </si>
+  <si>
+    <t>00:35:53</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ngk-xmi1epA</t>
+  </si>
+  <si>
+    <t>03:16:22</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1A-ADuKLKxw</t>
+  </si>
+  <si>
+    <t>02:39:16</t>
   </si>
 </sst>
 </file>
@@ -402,8 +1365,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr customHeight="1"/>
+  <dimension ref="A1:C163"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -423,10 +1391,1783 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26">
         <v>1</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B82" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" t="s">
+        <v>174</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>175</v>
+      </c>
+      <c r="B88" t="s">
+        <v>176</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>179</v>
+      </c>
+      <c r="B90" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" t="s">
+        <v>182</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" t="s">
+        <v>188</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>189</v>
+      </c>
+      <c r="B95" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>191</v>
+      </c>
+      <c r="B96" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>193</v>
+      </c>
+      <c r="B97" t="s">
+        <v>194</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>195</v>
+      </c>
+      <c r="B98" t="s">
+        <v>196</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>197</v>
+      </c>
+      <c r="B99" t="s">
+        <v>198</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>199</v>
+      </c>
+      <c r="B100" t="s">
+        <v>200</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>201</v>
+      </c>
+      <c r="B101" t="s">
+        <v>202</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>203</v>
+      </c>
+      <c r="B102" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>205</v>
+      </c>
+      <c r="B103" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>209</v>
+      </c>
+      <c r="B105" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>211</v>
+      </c>
+      <c r="B106" t="s">
+        <v>212</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>213</v>
+      </c>
+      <c r="B107" t="s">
+        <v>214</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>215</v>
+      </c>
+      <c r="B108" t="s">
+        <v>216</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>217</v>
+      </c>
+      <c r="B109" t="s">
+        <v>218</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>219</v>
+      </c>
+      <c r="B110" t="s">
+        <v>220</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>221</v>
+      </c>
+      <c r="B111" t="s">
+        <v>222</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>223</v>
+      </c>
+      <c r="B112" t="s">
+        <v>224</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>225</v>
+      </c>
+      <c r="B113" t="s">
+        <v>226</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>227</v>
+      </c>
+      <c r="B114" t="s">
+        <v>228</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>229</v>
+      </c>
+      <c r="B115" t="s">
+        <v>230</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>231</v>
+      </c>
+      <c r="B116" t="s">
+        <v>232</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>233</v>
+      </c>
+      <c r="B117" t="s">
+        <v>234</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>235</v>
+      </c>
+      <c r="B118" t="s">
+        <v>236</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>237</v>
+      </c>
+      <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" t="s">
+        <v>239</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" t="s">
+        <v>241</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
+        <v>243</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" t="s">
+        <v>245</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" t="s">
+        <v>247</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" t="s">
+        <v>249</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" t="s">
+        <v>251</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" t="s">
+        <v>253</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" t="s">
+        <v>255</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" t="s">
+        <v>257</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" t="s">
+        <v>259</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" t="s">
+        <v>261</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" t="s">
+        <v>263</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" t="s">
+        <v>267</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>268</v>
+      </c>
+      <c r="B135" t="s">
+        <v>269</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" t="s">
+        <v>271</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" t="s">
+        <v>273</v>
+      </c>
+      <c r="C137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" t="s">
+        <v>275</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>276</v>
+      </c>
+      <c r="B139" t="s">
+        <v>277</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>278</v>
+      </c>
+      <c r="B140" t="s">
+        <v>279</v>
+      </c>
+      <c r="C140" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>280</v>
+      </c>
+      <c r="B141" t="s">
+        <v>281</v>
+      </c>
+      <c r="C141" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>282</v>
+      </c>
+      <c r="B142" t="s">
+        <v>283</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>284</v>
+      </c>
+      <c r="B143" t="s">
+        <v>285</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" t="s">
+        <v>287</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" t="s">
+        <v>289</v>
+      </c>
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" t="s">
+        <v>291</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" t="s">
+        <v>293</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" t="s">
+        <v>295</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" t="s">
+        <v>297</v>
+      </c>
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>298</v>
+      </c>
+      <c r="B150" t="s">
+        <v>299</v>
+      </c>
+      <c r="C150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" t="s">
+        <v>301</v>
+      </c>
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>302</v>
+      </c>
+      <c r="B152" t="s">
+        <v>303</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>304</v>
+      </c>
+      <c r="B153" t="s">
+        <v>305</v>
+      </c>
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>306</v>
+      </c>
+      <c r="B154" t="s">
+        <v>307</v>
+      </c>
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>308</v>
+      </c>
+      <c r="B155" t="s">
+        <v>309</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" t="s">
+        <v>313</v>
+      </c>
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>314</v>
+      </c>
+      <c r="B158" t="s">
+        <v>315</v>
+      </c>
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+      <c r="B159" t="s">
+        <v>317</v>
+      </c>
+      <c r="C159" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>318</v>
+      </c>
+      <c r="B160" t="s">
+        <v>319</v>
+      </c>
+      <c r="C160" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>320</v>
+      </c>
+      <c r="B161" t="s">
+        <v>321</v>
+      </c>
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162" t="s">
+        <v>323</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>324</v>
+      </c>
+      <c r="B163" t="s">
+        <v>325</v>
+      </c>
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>